--- a/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263603970417151</v>
+        <v>1.25377667589764</v>
       </c>
       <c r="C3" t="n">
-        <v>4.60722111212282</v>
+        <v>4.660039138611299</v>
       </c>
       <c r="D3" t="n">
-        <v>6.076375338476115</v>
+        <v>6.102676359472887</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94720042101609</v>
+        <v>12.01649217398183</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.405987267788473</v>
+        <v>1.380440115824662</v>
       </c>
       <c r="C4" t="n">
-        <v>5.052620087467487</v>
+        <v>5.20661366770641</v>
       </c>
       <c r="D4" t="n">
-        <v>6.314833026773252</v>
+        <v>6.431149095457549</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77344038202921</v>
+        <v>13.01820287898862</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.611288262660006</v>
+        <v>1.547836657561191</v>
       </c>
       <c r="C5" t="n">
-        <v>5.653575685328345</v>
+        <v>5.906285549857254</v>
       </c>
       <c r="D5" t="n">
-        <v>6.570392445549177</v>
+        <v>6.893914737097272</v>
       </c>
       <c r="E5" t="n">
-        <v>13.83525639353753</v>
+        <v>14.34803694451572</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.851638846015439</v>
+        <v>1.732151750233724</v>
       </c>
       <c r="C6" t="n">
-        <v>6.374492193224728</v>
+        <v>6.773800210282306</v>
       </c>
       <c r="D6" t="n">
-        <v>6.842108169210561</v>
+        <v>7.355701792484001</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06823920845073</v>
+        <v>15.86165375300003</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.118683687257656</v>
+        <v>1.945980953771955</v>
       </c>
       <c r="C7" t="n">
-        <v>7.297949520179344</v>
+        <v>7.772731232763887</v>
       </c>
       <c r="D7" t="n">
-        <v>7.18739775027537</v>
+        <v>7.821763921587483</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60403095771237</v>
+        <v>17.54047610812333</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.339663605961106</v>
+        <v>1.173066356232798</v>
       </c>
       <c r="C8" t="n">
-        <v>5.087894074578245</v>
+        <v>5.385405060694886</v>
       </c>
       <c r="D8" t="n">
-        <v>5.396942125484682</v>
+        <v>6.111484738297842</v>
       </c>
       <c r="E8" t="n">
-        <v>11.82449980602403</v>
+        <v>12.66995615522553</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.697532033572972</v>
+        <v>1.455406398913587</v>
       </c>
       <c r="C9" t="n">
-        <v>6.429004325969648</v>
+        <v>6.566901450266344</v>
       </c>
       <c r="D9" t="n">
-        <v>5.868418195771642</v>
+        <v>6.770864639113303</v>
       </c>
       <c r="E9" t="n">
-        <v>13.99495455531426</v>
+        <v>14.79317248829323</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.060911134332292</v>
+        <v>1.757224822673556</v>
       </c>
       <c r="C10" t="n">
-        <v>7.991079358211649</v>
+        <v>7.84695546098749</v>
       </c>
       <c r="D10" t="n">
-        <v>6.275907457837378</v>
+        <v>7.36451432516285</v>
       </c>
       <c r="E10" t="n">
-        <v>16.32789795038132</v>
+        <v>16.9686946088239</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.425234012518712</v>
+        <v>2.072019249546244</v>
       </c>
       <c r="C11" t="n">
-        <v>9.7131714831972</v>
+        <v>9.232580384069843</v>
       </c>
       <c r="D11" t="n">
-        <v>6.682852063389508</v>
+        <v>8.019073777745806</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82125755910542</v>
+        <v>19.32367341136189</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.800592537404309</v>
+        <v>2.380946957880075</v>
       </c>
       <c r="C12" t="n">
-        <v>11.54499146359076</v>
+        <v>10.69599687481732</v>
       </c>
       <c r="D12" t="n">
-        <v>7.098153875688453</v>
+        <v>8.628309844524283</v>
       </c>
       <c r="E12" t="n">
-        <v>21.44373787668352</v>
+        <v>21.70525367722168</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.149123624573527</v>
+        <v>2.670459554877945</v>
       </c>
       <c r="C13" t="n">
-        <v>13.3989476756051</v>
+        <v>12.19379720859721</v>
       </c>
       <c r="D13" t="n">
-        <v>7.577239329185699</v>
+        <v>9.272785948785351</v>
       </c>
       <c r="E13" t="n">
-        <v>24.12531062936432</v>
+        <v>24.13704271226051</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.817087373359294</v>
+        <v>1.533970970408599</v>
       </c>
       <c r="C14" t="n">
-        <v>9.250458838403317</v>
+        <v>8.617555545906525</v>
       </c>
       <c r="D14" t="n">
-        <v>5.763055373469626</v>
+        <v>7.016295587848849</v>
       </c>
       <c r="E14" t="n">
-        <v>16.83060158523224</v>
+        <v>17.16782210416397</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.86002901794305</v>
+        <v>1.560861040027919</v>
       </c>
       <c r="C15" t="n">
-        <v>10.19853259639446</v>
+        <v>9.229714509412581</v>
       </c>
       <c r="D15" t="n">
-        <v>5.73709796416934</v>
+        <v>7.125191043203906</v>
       </c>
       <c r="E15" t="n">
-        <v>17.79565957850685</v>
+        <v>17.91576659264441</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.15068524326236</v>
+        <v>1.810499846263798</v>
       </c>
       <c r="C16" t="n">
-        <v>12.16745706969257</v>
+        <v>10.87733259406479</v>
       </c>
       <c r="D16" t="n">
-        <v>6.14306045735244</v>
+        <v>7.701486763073827</v>
       </c>
       <c r="E16" t="n">
-        <v>20.46120277030737</v>
+        <v>20.38931920340242</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.713355910928576</v>
+        <v>1.457424101908475</v>
       </c>
       <c r="C17" t="n">
-        <v>11.33451286497845</v>
+        <v>10.0011424029786</v>
       </c>
       <c r="D17" t="n">
-        <v>5.667040447994289</v>
+        <v>7.223375631105631</v>
       </c>
       <c r="E17" t="n">
-        <v>18.71490922390131</v>
+        <v>18.6819421359927</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.942397650329357</v>
+        <v>1.66357148484622</v>
       </c>
       <c r="C18" t="n">
-        <v>13.28376311428344</v>
+        <v>11.68531095465991</v>
       </c>
       <c r="D18" t="n">
-        <v>6.029707867420102</v>
+        <v>7.738802993312246</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2558686320329</v>
+        <v>21.08768543281838</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.933345936496202</v>
+        <v>1.667567198002505</v>
       </c>
       <c r="C19" t="n">
-        <v>14.24977340283118</v>
+        <v>12.51741085634839</v>
       </c>
       <c r="D19" t="n">
-        <v>6.075908914381958</v>
+        <v>7.880223750109002</v>
       </c>
       <c r="E19" t="n">
-        <v>22.25902825370934</v>
+        <v>22.06520180445989</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.133573380777338</v>
+        <v>1.844900285820606</v>
       </c>
       <c r="C20" t="n">
-        <v>16.32449100873892</v>
+        <v>14.40262170290537</v>
       </c>
       <c r="D20" t="n">
-        <v>6.415927414270797</v>
+        <v>8.374072297776273</v>
       </c>
       <c r="E20" t="n">
-        <v>24.87399180378706</v>
+        <v>24.62159428650224</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.257206475104381</v>
+        <v>1.093117163816569</v>
       </c>
       <c r="C21" t="n">
-        <v>11.89997990767052</v>
+        <v>10.6518251463993</v>
       </c>
       <c r="D21" t="n">
-        <v>5.323016417472121</v>
+        <v>7.0207919923343</v>
       </c>
       <c r="E21" t="n">
-        <v>18.48020280024702</v>
+        <v>18.76573430255017</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25377667589764</v>
+        <v>1.289158863158695</v>
       </c>
       <c r="C3" t="n">
-        <v>4.660039138611299</v>
+        <v>4.583040666167221</v>
       </c>
       <c r="D3" t="n">
-        <v>6.102676359472887</v>
+        <v>6.062758497818211</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01649217398183</v>
+        <v>11.93495802714413</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380440115824662</v>
+        <v>1.468889948332036</v>
       </c>
       <c r="C4" t="n">
-        <v>5.20661366770641</v>
+        <v>4.983830229341507</v>
       </c>
       <c r="D4" t="n">
-        <v>6.431149095457549</v>
+        <v>6.29802575373919</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01820287898862</v>
+        <v>12.75074593141273</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.547836657561191</v>
+        <v>1.698876725290512</v>
       </c>
       <c r="C5" t="n">
-        <v>5.906285549857254</v>
+        <v>5.454406916189766</v>
       </c>
       <c r="D5" t="n">
-        <v>6.893914737097272</v>
+        <v>6.593140960895449</v>
       </c>
       <c r="E5" t="n">
-        <v>14.34803694451572</v>
+        <v>13.74642460237573</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.732151750233724</v>
+        <v>1.949504734390727</v>
       </c>
       <c r="C6" t="n">
-        <v>6.773800210282306</v>
+        <v>6.027301819699519</v>
       </c>
       <c r="D6" t="n">
-        <v>7.355701792484001</v>
+        <v>6.921185602961614</v>
       </c>
       <c r="E6" t="n">
-        <v>15.86165375300003</v>
+        <v>14.89799215705186</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.945980953771955</v>
+        <v>2.233835572662663</v>
       </c>
       <c r="C7" t="n">
-        <v>7.772731232763887</v>
+        <v>6.673940225274426</v>
       </c>
       <c r="D7" t="n">
-        <v>7.821763921587483</v>
+        <v>7.238707717787566</v>
       </c>
       <c r="E7" t="n">
-        <v>17.54047610812333</v>
+        <v>16.14648351572465</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.173066356232798</v>
+        <v>1.413304444158283</v>
       </c>
       <c r="C8" t="n">
-        <v>5.385405060694886</v>
+        <v>4.2809607505007</v>
       </c>
       <c r="D8" t="n">
-        <v>6.111484738297842</v>
+        <v>5.580818518927807</v>
       </c>
       <c r="E8" t="n">
-        <v>12.66995615522553</v>
+        <v>11.27508371358679</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.455406398913587</v>
+        <v>1.806421179075446</v>
       </c>
       <c r="C9" t="n">
-        <v>6.566901450266344</v>
+        <v>5.0888570501368</v>
       </c>
       <c r="D9" t="n">
-        <v>6.770864639113303</v>
+        <v>6.063392677452569</v>
       </c>
       <c r="E9" t="n">
-        <v>14.79317248829323</v>
+        <v>12.95867090666482</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.757224822673556</v>
+        <v>2.242415965098036</v>
       </c>
       <c r="C10" t="n">
-        <v>7.84695546098749</v>
+        <v>6.059478333092124</v>
       </c>
       <c r="D10" t="n">
-        <v>7.36451432516285</v>
+        <v>6.646300546900208</v>
       </c>
       <c r="E10" t="n">
-        <v>16.9686946088239</v>
+        <v>14.94819484509037</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.072019249546244</v>
+        <v>2.709961457548747</v>
       </c>
       <c r="C11" t="n">
-        <v>9.232580384069843</v>
+        <v>7.203574687627089</v>
       </c>
       <c r="D11" t="n">
-        <v>8.019073777745806</v>
+        <v>7.173001747221323</v>
       </c>
       <c r="E11" t="n">
-        <v>19.32367341136189</v>
+        <v>17.08653789239716</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.380946957880075</v>
+        <v>3.210871956016159</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69599687481732</v>
+        <v>8.524627360922006</v>
       </c>
       <c r="D12" t="n">
-        <v>8.628309844524283</v>
+        <v>7.772532553102254</v>
       </c>
       <c r="E12" t="n">
-        <v>21.70525367722168</v>
+        <v>19.50803187004042</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.670459554877945</v>
+        <v>3.704481987767694</v>
       </c>
       <c r="C13" t="n">
-        <v>12.19379720859721</v>
+        <v>9.927643069134042</v>
       </c>
       <c r="D13" t="n">
-        <v>9.272785948785351</v>
+        <v>8.402998026702614</v>
       </c>
       <c r="E13" t="n">
-        <v>24.13704271226051</v>
+        <v>22.03512308360435</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.533970970408599</v>
+        <v>2.144549320110817</v>
       </c>
       <c r="C14" t="n">
-        <v>8.617555545906525</v>
+        <v>7.130109599202183</v>
       </c>
       <c r="D14" t="n">
-        <v>7.016295587848849</v>
+        <v>6.433647960332453</v>
       </c>
       <c r="E14" t="n">
-        <v>17.16782210416397</v>
+        <v>15.70830687964545</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.560861040027919</v>
+        <v>2.257980449859494</v>
       </c>
       <c r="C15" t="n">
-        <v>9.229714509412581</v>
+        <v>7.794870604701782</v>
       </c>
       <c r="D15" t="n">
-        <v>7.125191043203906</v>
+        <v>6.511451465894012</v>
       </c>
       <c r="E15" t="n">
-        <v>17.91576659264441</v>
+        <v>16.56430252045529</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.810499846263798</v>
+        <v>2.681270790022549</v>
       </c>
       <c r="C16" t="n">
-        <v>10.87733259406479</v>
+        <v>9.306477362407639</v>
       </c>
       <c r="D16" t="n">
-        <v>7.701486763073827</v>
+        <v>7.052620252905982</v>
       </c>
       <c r="E16" t="n">
-        <v>20.38931920340242</v>
+        <v>19.04036840533617</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.457424101908475</v>
+        <v>2.188109465748249</v>
       </c>
       <c r="C17" t="n">
-        <v>10.0011424029786</v>
+        <v>8.74613504273173</v>
       </c>
       <c r="D17" t="n">
-        <v>7.223375631105631</v>
+        <v>6.610382182050963</v>
       </c>
       <c r="E17" t="n">
-        <v>18.6819421359927</v>
+        <v>17.54462669053094</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.66357148484622</v>
+        <v>2.539368976850715</v>
       </c>
       <c r="C18" t="n">
-        <v>11.68531095465991</v>
+        <v>10.24135643125371</v>
       </c>
       <c r="D18" t="n">
-        <v>7.738802993312246</v>
+        <v>7.131444776079958</v>
       </c>
       <c r="E18" t="n">
-        <v>21.08768543281838</v>
+        <v>19.91217018418438</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.667567198002505</v>
+        <v>2.587474614358809</v>
       </c>
       <c r="C19" t="n">
-        <v>12.51741085634839</v>
+        <v>10.97043172885852</v>
       </c>
       <c r="D19" t="n">
-        <v>7.880223750109002</v>
+        <v>7.290065752655115</v>
       </c>
       <c r="E19" t="n">
-        <v>22.06520180445989</v>
+        <v>20.84797209587244</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.844900285820606</v>
+        <v>2.926236477186213</v>
       </c>
       <c r="C20" t="n">
-        <v>14.40262170290537</v>
+        <v>12.63055727926283</v>
       </c>
       <c r="D20" t="n">
-        <v>8.374072297776273</v>
+        <v>7.797815847814524</v>
       </c>
       <c r="E20" t="n">
-        <v>24.62159428650224</v>
+        <v>23.35460960426357</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.093117163816569</v>
+        <v>1.761235746464693</v>
       </c>
       <c r="C21" t="n">
-        <v>10.6518251463993</v>
+        <v>9.271144262531797</v>
       </c>
       <c r="D21" t="n">
-        <v>7.0207919923343</v>
+        <v>6.544781800453191</v>
       </c>
       <c r="E21" t="n">
-        <v>18.76573430255017</v>
+        <v>17.57716180944968</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_3_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.289158863158695</v>
+        <v>2.60991688876142</v>
       </c>
       <c r="C3" t="n">
-        <v>4.583040666167221</v>
+        <v>7.704183738617012</v>
       </c>
       <c r="D3" t="n">
-        <v>6.062758497818211</v>
+        <v>8.196481760612489</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93495802714413</v>
+        <v>18.51058238799092</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.468889948332036</v>
+        <v>1.113212290263661</v>
       </c>
       <c r="C4" t="n">
-        <v>4.983830229341507</v>
+        <v>4.504880373779708</v>
       </c>
       <c r="D4" t="n">
-        <v>6.29802575373919</v>
+        <v>5.74842724940576</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75074593141273</v>
+        <v>11.36651991344913</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.698876725290512</v>
+        <v>1.242676261480157</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454406916189766</v>
+        <v>5.152653012214639</v>
       </c>
       <c r="D5" t="n">
-        <v>6.593140960895449</v>
+        <v>6.008346728977362</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74642460237573</v>
+        <v>12.40367600267216</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.949504734390727</v>
+        <v>1.386750646116863</v>
       </c>
       <c r="C6" t="n">
-        <v>6.027301819699519</v>
+        <v>5.987807778621252</v>
       </c>
       <c r="D6" t="n">
-        <v>6.921185602961614</v>
+        <v>6.320827577312769</v>
       </c>
       <c r="E6" t="n">
-        <v>14.89799215705186</v>
+        <v>13.69538600205088</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.233835572662663</v>
+        <v>1.54320210709874</v>
       </c>
       <c r="C7" t="n">
-        <v>6.673940225274426</v>
+        <v>6.990364584180839</v>
       </c>
       <c r="D7" t="n">
-        <v>7.238707717787566</v>
+        <v>6.656315110329597</v>
       </c>
       <c r="E7" t="n">
-        <v>16.14648351572465</v>
+        <v>15.18988180160918</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.413304444158283</v>
+        <v>1.704143956689532</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2809607505007</v>
+        <v>8.121586020758029</v>
       </c>
       <c r="D8" t="n">
-        <v>5.580818518927807</v>
+        <v>7.086612476972226</v>
       </c>
       <c r="E8" t="n">
-        <v>11.27508371358679</v>
+        <v>16.91234245441979</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.806421179075446</v>
+        <v>1.867569634602071</v>
       </c>
       <c r="C9" t="n">
-        <v>5.0888570501368</v>
+        <v>9.385025391722086</v>
       </c>
       <c r="D9" t="n">
-        <v>6.063392677452569</v>
+        <v>7.607340341766792</v>
       </c>
       <c r="E9" t="n">
-        <v>12.95867090666482</v>
+        <v>18.85993536809095</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.242415965098036</v>
+        <v>1.150176340387393</v>
       </c>
       <c r="C10" t="n">
-        <v>6.059478333092124</v>
+        <v>6.913830579956609</v>
       </c>
       <c r="D10" t="n">
-        <v>6.646300546900208</v>
+        <v>6.014451508096107</v>
       </c>
       <c r="E10" t="n">
-        <v>14.94819484509037</v>
+        <v>14.07845842844011</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.709961457548747</v>
+        <v>1.103769126407646</v>
       </c>
       <c r="C11" t="n">
-        <v>7.203574687627089</v>
+        <v>7.348833170231329</v>
       </c>
       <c r="D11" t="n">
-        <v>7.173001747221323</v>
+        <v>5.911210919517513</v>
       </c>
       <c r="E11" t="n">
-        <v>17.08653789239716</v>
+        <v>14.36381321615649</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.210871956016159</v>
+        <v>1.215492015150933</v>
       </c>
       <c r="C12" t="n">
-        <v>8.524627360922006</v>
+        <v>8.67951364352154</v>
       </c>
       <c r="D12" t="n">
-        <v>7.772532553102254</v>
+        <v>6.332891193445603</v>
       </c>
       <c r="E12" t="n">
-        <v>19.50803187004042</v>
+        <v>16.22789685211808</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.704481987767694</v>
+        <v>0.9702808910612077</v>
       </c>
       <c r="C13" t="n">
-        <v>9.927643069134042</v>
+        <v>8.252207955248117</v>
       </c>
       <c r="D13" t="n">
-        <v>8.402998026702614</v>
+        <v>5.823187420354743</v>
       </c>
       <c r="E13" t="n">
-        <v>22.03512308360435</v>
+        <v>15.04567626666407</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.144549320110817</v>
+        <v>1.064499218237774</v>
       </c>
       <c r="C14" t="n">
-        <v>7.130109599202183</v>
+        <v>9.63774849025164</v>
       </c>
       <c r="D14" t="n">
-        <v>6.433647960332453</v>
+        <v>6.182781969466265</v>
       </c>
       <c r="E14" t="n">
-        <v>15.70830687964545</v>
+        <v>16.88502967795568</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.257980449859494</v>
+        <v>1.042105553103905</v>
       </c>
       <c r="C15" t="n">
-        <v>7.794870604701782</v>
+        <v>10.38303244245356</v>
       </c>
       <c r="D15" t="n">
-        <v>6.511451465894012</v>
+        <v>6.263903782268179</v>
       </c>
       <c r="E15" t="n">
-        <v>16.56430252045529</v>
+        <v>17.68904177782565</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.681270790022549</v>
+        <v>1.149871998599077</v>
       </c>
       <c r="C16" t="n">
-        <v>9.306477362407639</v>
+        <v>12.11080040968048</v>
       </c>
       <c r="D16" t="n">
-        <v>7.052620252905982</v>
+        <v>6.690188452929187</v>
       </c>
       <c r="E16" t="n">
-        <v>19.04036840533617</v>
+        <v>19.95086086120875</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.188109465748249</v>
+        <v>0.6913663682846888</v>
       </c>
       <c r="C17" t="n">
-        <v>8.74613504273173</v>
+        <v>9.058831504011383</v>
       </c>
       <c r="D17" t="n">
-        <v>6.610382182050963</v>
+        <v>5.579124941078986</v>
       </c>
       <c r="E17" t="n">
-        <v>17.54462669053094</v>
+        <v>15.32932281337506</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.539368976850715</v>
+        <v>0.5548739849632549</v>
       </c>
       <c r="C18" t="n">
-        <v>10.24135643125371</v>
+        <v>8.03679287398228</v>
       </c>
       <c r="D18" t="n">
-        <v>7.131444776079958</v>
+        <v>5.10403759203987</v>
       </c>
       <c r="E18" t="n">
-        <v>19.91217018418438</v>
+        <v>13.6957044509854</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.587474614358809</v>
+        <v>0.657015016113093</v>
       </c>
       <c r="C19" t="n">
-        <v>10.97043172885852</v>
+        <v>9.933725788127969</v>
       </c>
       <c r="D19" t="n">
-        <v>7.290065752655115</v>
+        <v>5.62726984849525</v>
       </c>
       <c r="E19" t="n">
-        <v>20.84797209587244</v>
+        <v>16.21801065273631</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.926236477186213</v>
+        <v>0.7491029507714438</v>
       </c>
       <c r="C20" t="n">
-        <v>12.63055727926283</v>
+        <v>11.90906107393481</v>
       </c>
       <c r="D20" t="n">
-        <v>7.797815847814524</v>
+        <v>6.146781281151536</v>
       </c>
       <c r="E20" t="n">
-        <v>23.35460960426357</v>
+        <v>18.80494530585779</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.761235746464693</v>
+        <v>0.8374111567684444</v>
       </c>
       <c r="C21" t="n">
-        <v>9.271144262531797</v>
+        <v>13.91405495788694</v>
       </c>
       <c r="D21" t="n">
-        <v>6.544781800453191</v>
+        <v>6.612512574569178</v>
       </c>
       <c r="E21" t="n">
-        <v>17.57716180944968</v>
+        <v>21.36397868922456</v>
       </c>
     </row>
   </sheetData>
